--- a/modeles/performances_modeles.xlsx
+++ b/modeles/performances_modeles.xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6554054054054054</v>
+        <v>0.6418918918918919</v>
       </c>
       <c r="C2" t="n">
         <v>0.7171717171717171</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4641148325358851</v>
+        <v>0.4589371980676328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5434173669467787</v>
+        <v>0.5352112676056338</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7678303303303304</v>
+        <v>0.7533271908271908</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5569858936052914</v>
+        <v>0.550903673169217</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2006391994774515</v>
+        <v>0.2018577628715015</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5700000000000003</v>
+        <v>0.5600000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6554054054054054</v>
+        <v>0.5540540540540541</v>
       </c>
       <c r="C3" t="n">
         <v>0.7727272727272727</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5187165775401069</v>
+        <v>0.4767441860465116</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5791044776119403</v>
+        <v>0.5125</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7750819000819001</v>
+        <v>0.7440281190281191</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5525657820372009</v>
+        <v>0.5382839795010335</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1995417920456778</v>
+        <v>0.1948166925063578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5000000000000002</v>
+        <v>0.5200000000000002</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2905405405405405</v>
+        <v>0.3243243243243243</v>
       </c>
       <c r="C4" t="n">
         <v>0.9570707070707071</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.7384615384615385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4134615384615384</v>
+        <v>0.4507042253521127</v>
       </c>
       <c r="F4" t="n">
-        <v>0.767949767949768</v>
+        <v>0.7534636909636909</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5556836236255458</v>
+        <v>0.5492188981679338</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1615405287270204</v>
+        <v>0.1620685292689652</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3300000000000001</v>
+        <v>0.3200000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6486486486486487</v>
+        <v>0.6351351351351351</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7095959595959596</v>
+        <v>0.7146464646464646</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4549763033175355</v>
+        <v>0.4541062801932367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5348189415041783</v>
+        <v>0.5295774647887324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7497952497952498</v>
+        <v>0.7309326371826371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5371852480136197</v>
+        <v>0.5323834932975727</v>
       </c>
       <c r="H5" t="n">
-        <v>0.200491264462471</v>
+        <v>0.2017050385475159</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5500000000000003</v>
+        <v>0.5700000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/modeles/performances_modeles.xlsx
+++ b/modeles/performances_modeles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Score composite</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Seuil optimal</t>
         </is>
       </c>
@@ -482,28 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6418918918918919</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7171717171717171</v>
+        <v>0.8434343434343434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4589371980676328</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5352112676056338</v>
+        <v>0.5314685314685315</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7533271908271908</v>
+        <v>0.7607067294567296</v>
       </c>
       <c r="G2" t="n">
-        <v>0.550903673169217</v>
+        <v>0.5490358841670169</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2018577628715015</v>
+        <v>0.1998676384934421</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5600000000000003</v>
+        <v>0.6695912449598868</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5800000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5540540540540541</v>
+        <v>0.6148648648648649</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.8005050505050505</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4767441860465116</v>
+        <v>0.5352941176470588</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5125</v>
+        <v>0.5723270440251572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7440281190281191</v>
+        <v>0.7606726044226044</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5382839795010335</v>
+        <v>0.5474789994265754</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1948166925063578</v>
+        <v>0.1948384128711323</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5200000000000002</v>
+        <v>0.6773295373325036</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5000000000000002</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3243243243243243</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9570707070707071</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7384615384615385</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4507042253521127</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7534636909636909</v>
+        <v>0.7626006688506688</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5492188981679338</v>
+        <v>0.550225415019167</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1620685292689652</v>
+        <v>0.1611786563777481</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.6706699666440766</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2900000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6351351351351351</v>
+        <v>0.6283783783783784</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7146464646464646</v>
+        <v>0.7929292929292929</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4541062801932367</v>
+        <v>0.5314285714285715</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5295774647887324</v>
+        <v>0.5758513931888545</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7309326371826371</v>
+        <v>0.751748907998908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5323834932975727</v>
+        <v>0.5369405983378899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2017050385475159</v>
+        <v>0.1963230818510056</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5700000000000003</v>
+        <v>0.6741837778703393</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5300000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/modeles/performances_modeles.xlsx
+++ b/modeles/performances_modeles.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparaison modeles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,31 +488,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5135135135135135</v>
+        <v>0.5202702702702703</v>
       </c>
       <c r="C2" t="n">
         <v>0.8434343434343434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5507246376811594</v>
+        <v>0.5539568345323741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5314685314685315</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7607067294567296</v>
+        <v>0.7600924788424788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5490358841670169</v>
+        <v>0.5555525781012576</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1998676384934421</v>
+        <v>0.1604638784020466</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6695912449598868</v>
+        <v>0.6788071044631129</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5800000000000003</v>
+        <v>0.3500000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +522,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6148648648648649</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8005050505050505</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5352941176470588</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5723270440251572</v>
+        <v>0.5623003194888179</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7606726044226044</v>
+        <v>0.7627371689871691</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5474789994265754</v>
+        <v>0.5504580622053984</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1948384128711323</v>
+        <v>0.161918125513963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6773295373325036</v>
+        <v>0.6807934315270147</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5000000000000002</v>
+        <v>0.3300000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +568,19 @@
         <v>0.5432098765432098</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7626006688506688</v>
+        <v>0.7601521976521977</v>
       </c>
       <c r="G4" t="n">
-        <v>0.550225415019167</v>
+        <v>0.5441574448231412</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1611786563777481</v>
+        <v>0.162273306718669</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6706699666440766</v>
+        <v>0.669068118021507</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2900000000000001</v>
+        <v>0.3000000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +590,172 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6283783783783784</v>
+        <v>0.6081081081081081</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7929292929292929</v>
+        <v>0.8005050505050505</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5314285714285715</v>
+        <v>0.5325443786982249</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5758513931888545</v>
+        <v>0.5678233438485805</v>
       </c>
       <c r="F5" t="n">
-        <v>0.751748907998908</v>
+        <v>0.7512114387114387</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5369405983378899</v>
+        <v>0.5320107405729051</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1963230818510056</v>
+        <v>0.1654510918889982</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6741837778703393</v>
+        <v>0.6764881041177881</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5300000000000002</v>
+        <v>0.3300000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Probabilité moyenne prédite</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fréquence réelle observée</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Écart absolu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.05428422168873903</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01792058532510267</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.1185006773535651</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.009409768262656007</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.1468725285566127</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.003127471443387264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.1720128077459512</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07288515143772223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.2003575995749837</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.05660377358490566</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1437538259900781</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.2450385382570077</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.02281631603478551</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.301216318345604</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2909090909090909</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01030722743651308</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.3580361943035026</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1234452871779789</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.4526312912410757</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4074074074074074</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.04522388383366832</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.7257424782417388</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001530249030988529</v>
       </c>
     </row>
   </sheetData>
